--- a/LISTAS_ORDENADAS/MA/Tenders Bnaqueta Barral/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MA/Tenders Bnaqueta Barral/BANQUETA ESCALERA Y TAPIZADA DISMAY.xlsx
@@ -903,14 +903,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="27" t="n">
-        <v>45202.60861944905</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -962,16 +958,6 @@
       <c r="C12" s="41" t="n"/>
       <c r="D12" s="41" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -1026,10 +1012,8 @@
         </is>
       </c>
       <c r="C29" s="42" t="n"/>
-      <c r="D29" s="44" t="inlineStr">
-        <is>
-          <t>********************</t>
-        </is>
+      <c r="D29" s="44" t="n">
+        <v>8715.088</v>
       </c>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="17">
@@ -1045,7 +1029,7 @@
       </c>
       <c r="C30" s="42" t="n"/>
       <c r="D30" s="44" t="n">
-        <v>3077.81</v>
+        <v>3077.813</v>
       </c>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="17">
@@ -1065,8 +1049,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
     <row r="35" ht="18" customHeight="1" s="17">
       <c r="A35" s="29" t="n"/>
       <c r="B35" s="29" t="n"/>
@@ -1079,34 +1061,29 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B31:C31"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
